--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/lda_env_significance.xlsx
@@ -466,17 +466,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>p &lt; 0.01**</t>
+          <t>p &lt; 0.001***</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.12 ± 0.50</t>
+          <t>1.72 ± 0.35</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.71 ± 0.25</t>
+          <t>1.38 ± 0.13</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>Velocity  at bottom (m/sec)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -501,17 +501,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.08 ± 1.09</t>
+          <t>0.41 ± 0.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.89 ± 0.62</t>
+          <t>0.19 ± 0.03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.50 ± 0.07</t>
+          <t>0.10 ± 0.01</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Velocity  at bottom (m/sec)</t>
+          <t>Water DO Bottom (mg/L)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,17 +531,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.43 ± 0.04</t>
+          <t>8.76 ± 0.38</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.22 ± 0.03</t>
+          <t>9.18 ± 0.34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.10 ± 0.01</t>
+          <t>10.29 ± 0.27</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Water DO Bottom (mg/L)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,17 +561,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.58 ± 0.38</t>
+          <t>8.46 ± 1.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.12 ± 0.30</t>
+          <t>3.76 ± 0.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.29 ± 0.27</t>
+          <t>1.50 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -591,12 +591,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.79 ± 0.29</t>
+          <t>0.65 ± 0.28</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.92 ± 0.20</t>
+          <t>0.77 ± 0.22</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -621,12 +621,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.16 ± 0.67</t>
+          <t>18.07 ± 0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.22 ± 0.36</t>
+          <t>19.28 ± 0.39</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -656,10 +656,10 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
